--- a/happy_tea_captive_portal.xlsx
+++ b/happy_tea_captive_portal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,2433 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>77777777</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Té Verde</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hola</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1996-10-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>74123698</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>77777777</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Eueye</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>77777777</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dddd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>77777777</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Té Verde</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Qqqqq</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fdsfsdf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>77998877</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fdsfsdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>77998877</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fdsfsdf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>77998877</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fdsfsdf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>77998877</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fdsfsdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>77998877</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fdsfsdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>77998877</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dasdsad</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11234r</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>77551122</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fsdfsdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>77981111</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Qqwee</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>77112255</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>eqwe</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>eqwe</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>eqwe</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>eqwe</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>eqwe</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>eqwe</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>eqwe</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>77665544</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12312</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>77886655</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12312</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>77886655</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12312</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>77886655</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12312</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>77886655</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12312</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>77886655</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>rerer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>77887788</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>qwqw</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>77667766</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>qwqw</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>77667766</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>qwqw</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>77667766</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12233</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>77441144</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Qqwwj</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-10-12 14:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Whdjdjd</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>77447744</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-10-12 14:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wuewud</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>77777777</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-10-12 14:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dasdsa</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>77667766</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-10-12 14:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>yryrty</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>77566776</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-10-12 14:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Qqq</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-10-12 15:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Suwuw</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>77441144</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-10-12 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>qwqw</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>77667766</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-10-12 15:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Eueue</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-10-12 15:17:50</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>36:15:b5:e9:28:86</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Rurru</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-10-12 15:23:50</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>36:15:b5:e9:28:86</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Wuwuwjw</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>77447744</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025-10-12 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ssdjshs</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>77441111</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-10-12 16:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Qyqyq</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>77447744</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Wwww</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>77447777</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Yyyy</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ajsjsjs</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Qqwee</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>77411122</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:49</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>46:f0:0f:86:fb:25</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sjsjsjs</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>77998844</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:49</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>46:f0:0f:86:fb:25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sjsjsjs</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>77553366</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:53</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>46:f0:0f:86:fb:25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Kevv</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:57</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>36:15:b5:e9:28:86</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (Linux; Android 12; V2027 Build/SP1A.210812.003; wv) AppleWebKit/537.36 (KHTML, like Gecko) Version/4.0 Chrome/140.0.7339.208 Mobile Safari/537.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Wwwe</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>77981013</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2025-10-12 20:04</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>46:f0:0f:86:fb:25</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1ñwwww</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>77981013</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025-10-12 20:07</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>36:15:b5:e9:28:86</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (Linux; Android 12; V2027 Build/SP1A.210812.003; wv) AppleWebKit/537.36 (KHTML, like Gecko) Version/4.0 Chrome/140.0.7339.208 Mobile Safari/537.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Rrrrr</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>77553311</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2025-10-12 20:15</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>36:15:b5:e9:28:86</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (Linux; Android 12; V2027 Build/SP1A.210812.003; wv) AppleWebKit/537.36 (KHTML, like Gecko) Version/4.0 Chrome/140.0.7339.208 Mobile Safari/537.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Wwww</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>77941111</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025-10-12 20:16</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>46:f0:0f:86:fb:25</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Wwww</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>77113355</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Té Frutal</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2025-10-13 09:14</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>32:4d:0d:3b:5a:54</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (Macintosh; Intel Mac OS X 10_15_7) AppleWebKit/605.1.15 (KHTML, like Gecko)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Gilda</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1998-06-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>63985375</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2025-10-14 20:50</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5e:86:6d:97:bc:fa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Kee</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>77441144</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-10-14 21:24</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>46:f0:0f:86:fb:25</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Kee2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>77447711</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2025-10-14 21:36</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Qwe</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>77445577</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2025-10-14 21:53</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>77442200</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:19</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Shilda</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>63985375</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:19</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>5e:86:6d:97:bc:fa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>77669933</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ppo</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>77777777</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Té Verde</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:33</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Qqwrt</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>77445533</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:42</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Qqwrt</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>77445533</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Café Especial</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:42</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Quwue</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>77918244</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:52</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Www</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>77441122</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:54</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Werty</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>77447744</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Infusión Herbales</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2025-10-14 22:59</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Weew</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>74124578</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2025-10-14 23:04</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>da:f4:62:14:87:75</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
